--- a/www/download/IND.gdp.s.mv.rpO2.xlsx
+++ b/www/download/IND.gdp.s.mv.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12506.992</t>
+          <t>12506992140.2985</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12134.392</t>
+          <t>12134392016.5268</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12908.351</t>
+          <t>12908350575.9141</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12723.144</t>
+          <t>12723144001.4434</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13140.977</t>
+          <t>13140976663.8119</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13011.122</t>
+          <t>13011122003.7352</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14795.205</t>
+          <t>14795205137.6333</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13655.392</t>
+          <t>13655391940.8975</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15261.982</t>
+          <t>15261982361.1362</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24335.562</t>
+          <t>24335562210.9141</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>18343.752</t>
+          <t>18343751560.5153</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>17638.467</t>
+          <t>17638467258.0695</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>16021.435</t>
+          <t>16021434942.8993</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>17277.097</t>
+          <t>17277096597.1201</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>18248.187</t>
+          <t>18248186503.1219</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7317.906</t>
+          <t>7317906347.85936</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7314.886</t>
+          <t>7314885654.56053</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7146.327</t>
+          <t>7146327211.38438</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7181.826</t>
+          <t>7181826405.94365</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7695.306</t>
+          <t>7695305705.39018</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8143.076</t>
+          <t>8143075826.69545</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8208.201</t>
+          <t>8208200784.25608</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8518.964</t>
+          <t>8518963664.27915</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8751.142</t>
+          <t>8751142433.79308</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8980.581</t>
+          <t>8980581341.27881</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>8345.781</t>
+          <t>8345781374.03488</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>8146.283</t>
+          <t>8146282853.64322</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>8149.511</t>
+          <t>8149511220.52888</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>8062.663</t>
+          <t>8062662937.17401</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>8552.311</t>
+          <t>8552310958.90904</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12013.631</t>
+          <t>12013630936.8496</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12069.534</t>
+          <t>12069534329.7203</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12288.544</t>
+          <t>12288544316.7929</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12183.076</t>
+          <t>12183076273.1329</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12431.736</t>
+          <t>12431736049.6532</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12513.359</t>
+          <t>12513359491.2691</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12454.084</t>
+          <t>12454083887.2469</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12196.288</t>
+          <t>12196287734.2551</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12032.548</t>
+          <t>12032547505.8736</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12031.305</t>
+          <t>12031304790.5252</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12055.614</t>
+          <t>12055613517.9017</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12227.037</t>
+          <t>12227036857.5464</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>12458.064</t>
+          <t>12458063565.5624</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>12650.566</t>
+          <t>12650566379.9347</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>12477.404</t>
+          <t>12477404175.8537</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8054.339</t>
+          <t>8054339057.74963</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8773.753</t>
+          <t>8773752794.60396</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8891.416</t>
+          <t>8891415901.33083</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7209.66</t>
+          <t>7209660130.43475</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6756.961</t>
+          <t>6756961354.89886</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6306.004</t>
+          <t>6306003561.53269</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6898.108</t>
+          <t>6898108486.37493</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6732.564</t>
+          <t>6732563595.39943</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6206.488</t>
+          <t>6206487564.09396</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6102.254</t>
+          <t>6102254157.91293</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5766.874</t>
+          <t>5766873530.39553</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5395.104</t>
+          <t>5395104482.25452</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>5794.418</t>
+          <t>5794417847.85763</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6299.805</t>
+          <t>6299804749.86193</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>6058.105</t>
+          <t>6058105241.79902</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>406738.778</t>
+          <t>406738777631.694</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>389168.661</t>
+          <t>389168661164.816</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>387211.56</t>
+          <t>387211560483.25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>373544.646</t>
+          <t>373544645656.171</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>375471.643</t>
+          <t>375471642603.556</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>352055.625</t>
+          <t>352055625197.169</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>336408.689</t>
+          <t>336408689391.983</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>341707.861</t>
+          <t>341707860717.249</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>321937.312</t>
+          <t>321937311801.82</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>334869.829</t>
+          <t>334869828760.844</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>332204.331</t>
+          <t>332204331065.831</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>340390.44</t>
+          <t>340390440374.787</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>434899.39</t>
+          <t>434899389765.288</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>453042.095</t>
+          <t>453042095304.171</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>463826.94</t>
+          <t>463826939507.778</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>35193.733</t>
+          <t>35193733095.2968</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>34423.957</t>
+          <t>34423957099.2858</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31454.349</t>
+          <t>31454349495.4751</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31646.976</t>
+          <t>31646975841.7231</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>31865.057</t>
+          <t>31865056523.931</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>29886.755</t>
+          <t>29886754591.1391</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>31585.104</t>
+          <t>31585104400.8526</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31397.146</t>
+          <t>31397145616.4127</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31238.04</t>
+          <t>31238039892.1663</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>33088.654</t>
+          <t>33088654035.3302</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>31269.643</t>
+          <t>31269643130.7606</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>33652.816</t>
+          <t>33652815871.3085</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>35056.853</t>
+          <t>35056853317.574</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>36678.083</t>
+          <t>36678083060.6999</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>36865.504</t>
+          <t>36865503734.0815</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6424523.083</t>
+          <t>6424523083091.34</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6437807.793</t>
+          <t>6437807792878.54</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5783533.25</t>
+          <t>5783533250171.65</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5301264.152</t>
+          <t>5301264152088.43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4645998.028</t>
+          <t>4645998028000.09</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4719114.558</t>
+          <t>4719114558423.68</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5408808.148</t>
+          <t>5408808148461.28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5764914.65</t>
+          <t>5764914650343.71</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6419772.766</t>
+          <t>6419772766422.24</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7382165.645</t>
+          <t>7382165645117.81</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7820794.037</t>
+          <t>7820794036717.61</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7656394.992</t>
+          <t>7656394991714.01</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>8260683.389</t>
+          <t>8260683389370.55</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>8490601.753</t>
+          <t>8490601752800.33</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>8455131.257</t>
+          <t>8455131256990.34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>857.61</t>
+          <t>857610002.36317</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>825.085</t>
+          <t>825084509.901856</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>816.402</t>
+          <t>816401942.837377</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>795.234</t>
+          <t>795233511.142376</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>766.789</t>
+          <t>766789040.422837</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>723.263</t>
+          <t>723262531.101963</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>756.128</t>
+          <t>756127919.08795</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>796.052</t>
+          <t>796052457.799012</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>896.294</t>
+          <t>896294042.693925</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>953.516</t>
+          <t>953516351.957367</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>980.929</t>
+          <t>980929322.654476</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1090.594</t>
+          <t>1090594082.48453</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1163.364</t>
+          <t>1163363708.61777</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1189.666</t>
+          <t>1189665909.77482</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1255.443</t>
+          <t>1255442711.09491</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9323.588</t>
+          <t>9323587765.3897</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9448.86</t>
+          <t>9448860496.66348</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9341.593</t>
+          <t>9341592764.73091</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9586.949</t>
+          <t>9586949247.72723</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9448.822</t>
+          <t>9448822070.9096</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9471.973</t>
+          <t>9471972982.68026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8801.374</t>
+          <t>8801373983.88232</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8552.419</t>
+          <t>8552419136.26062</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8833.459</t>
+          <t>8833458678.46326</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8771.775</t>
+          <t>8771774884.13883</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>8801.808</t>
+          <t>8801808145.0447</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>8969.392</t>
+          <t>8969392307.36538</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>9192.116</t>
+          <t>9192115515.12637</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>9876.126</t>
+          <t>9876126291.89816</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>9261.091</t>
+          <t>9261091131.77251</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>63291.472</t>
+          <t>63291471828.7531</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>62725.623</t>
+          <t>62725623262.6268</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>60842.88</t>
+          <t>60842879564.2241</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61155.464</t>
+          <t>61155463815.3615</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>59803.064</t>
+          <t>59803063503.9446</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>59141.338</t>
+          <t>59141338347.4271</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>59104.273</t>
+          <t>59104272910.1893</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>58440.128</t>
+          <t>58440127820.9803</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>57089.806</t>
+          <t>57089806464.0175</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>58914.933</t>
+          <t>58914932977.2354</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>58175</t>
+          <t>58174999996.0518</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>58535.299</t>
+          <t>58535299382.0354</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>59345.162</t>
+          <t>59345161914.7564</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>60399.494</t>
+          <t>60399494469.0622</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>58315.861</t>
+          <t>58315860676.6641</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3798.502</t>
+          <t>3798501713.25438</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3897.94</t>
+          <t>3897939552.59674</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4132.781</t>
+          <t>4132781065.73301</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4772.958</t>
+          <t>4772957680.74326</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5006.437</t>
+          <t>5006436536.60586</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5142.03</t>
+          <t>5142029630.50357</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5367.241</t>
+          <t>5367240608.65051</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5462.269</t>
+          <t>5462268871.72783</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5460.194</t>
+          <t>5460193788.43355</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5413.865</t>
+          <t>5413865055.072</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>5549.615</t>
+          <t>5549614718.00688</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>6002.328</t>
+          <t>6002327778.35613</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>6223.812</t>
+          <t>6223811661.75453</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>5980.222</t>
+          <t>5980222295.1922</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5899.32</t>
+          <t>5899319736.67244</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30939.146</t>
+          <t>30939146250.7601</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30088.765</t>
+          <t>30088765305.3629</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29586.528</t>
+          <t>29586527898.4285</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30311.503</t>
+          <t>30311503439.5103</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>30860.544</t>
+          <t>30860543727.6651</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>30710.434</t>
+          <t>30710433855.8409</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31686.101</t>
+          <t>31686100544.2646</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>33527</t>
+          <t>33526999846.7101</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>35943.871</t>
+          <t>35943871107.8391</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>36989.911</t>
+          <t>36989910644.7542</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>37744.675</t>
+          <t>37744675074.8931</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>38576.029</t>
+          <t>38576029185.2435</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>39142.596</t>
+          <t>39142595752.1722</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>38992.708</t>
+          <t>38992708166.8782</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>35722.455</t>
+          <t>35722454750.1952</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7051.618</t>
+          <t>7051617517.85184</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6925.262</t>
+          <t>6925262229.07371</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11752.397</t>
+          <t>11752397197.5497</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12266.161</t>
+          <t>12266160586.2408</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1256.138</t>
+          <t>1256138241.06775</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1161.126</t>
+          <t>1161126335.69471</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1715.575</t>
+          <t>1715574642.1103</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1152.731</t>
+          <t>1152731430.22459</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1049.697</t>
+          <t>1049696909.84538</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1286.085</t>
+          <t>1286085241.9881</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1740.019</t>
+          <t>1740018704.96778</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1283.849</t>
+          <t>1283848609.04956</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1284.59</t>
+          <t>1284589588.16074</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1308.983</t>
+          <t>1308983332.6751</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>947.371</t>
+          <t>947371334.189205</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5193.41</t>
+          <t>5193410480.93968</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5184.315</t>
+          <t>5184315151.16519</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5371.402</t>
+          <t>5371402119.01097</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5425.965</t>
+          <t>5425964915.23588</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5459.977</t>
+          <t>5459977380.58931</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5466.772</t>
+          <t>5466771809.79718</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5384.482</t>
+          <t>5384482021.85392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5173.894</t>
+          <t>5173893584.05951</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4884.042</t>
+          <t>4884042483.90453</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4933.241</t>
+          <t>4933240628.47768</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5035.44</t>
+          <t>5035440489.46094</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5139.945</t>
+          <t>5139944631.84199</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>5199.003</t>
+          <t>5199002542.64097</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5845.182</t>
+          <t>5845181912.67044</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4935.779</t>
+          <t>4935778767.59681</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>30915.971</t>
+          <t>30915970673.1123</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30537.244</t>
+          <t>30537243780.0973</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30414.156</t>
+          <t>30414156229.3692</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32213.812</t>
+          <t>32213811972.9417</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>33341.159</t>
+          <t>33341159049.6054</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>32668.172</t>
+          <t>32668171765.8618</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>32175.266</t>
+          <t>32175266047.5011</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31257.665</t>
+          <t>31257665106.1917</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30791.936</t>
+          <t>30791935639.0669</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30360.437</t>
+          <t>30360437078.8638</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>30508.729</t>
+          <t>30508729184.3552</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>30514.621</t>
+          <t>30514621063.849</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>30680.575</t>
+          <t>30680574642.9084</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>30386.672</t>
+          <t>30386672416.3936</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>29538.378</t>
+          <t>29538378188.64</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>34987.972</t>
+          <t>34987971991.8945</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>37333.655</t>
+          <t>37333655127.1771</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41591.277</t>
+          <t>41591276669.0646</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41881.313</t>
+          <t>41881313468.2822</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>40073.077</t>
+          <t>40073077212.5723</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>38942.8</t>
+          <t>38942799543.2107</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>37876.791</t>
+          <t>37876790970.5005</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>39111.37</t>
+          <t>39111369892.0401</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>38956.802</t>
+          <t>38956801978.9201</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40535.607</t>
+          <t>40535606823.5309</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>41892.942</t>
+          <t>41892942469.8981</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>40843.748</t>
+          <t>40843748161.5659</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>39213.812</t>
+          <t>39213811510.2879</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>36856.004</t>
+          <t>36856003798.0181</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>33046.639</t>
+          <t>33046639458.1191</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9501.729</t>
+          <t>9501728504.51698</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9479.119</t>
+          <t>9479118969.95528</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10492.586</t>
+          <t>10492585647.6863</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10596.94</t>
+          <t>10596940464.4431</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10220.575</t>
+          <t>10220574873.6209</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9886.483</t>
+          <t>9886483421.80608</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8462.686</t>
+          <t>8462685529.63538</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8493.965</t>
+          <t>8493965089.56815</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8418.047</t>
+          <t>8418046750.99833</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9931.645</t>
+          <t>9931644883.70416</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7861.56</t>
+          <t>7861559869.4152</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9095.002</t>
+          <t>9095001634.81294</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>8898.829</t>
+          <t>8898829481.83324</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>8752.007</t>
+          <t>8752007365.67338</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8973.092</t>
+          <t>8973091701.56713</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9042.37</t>
+          <t>9042370024.08835</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8621.328</t>
+          <t>8621327855.279</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9887.662</t>
+          <t>9887661888.75651</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10078.327</t>
+          <t>10078327444.5241</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9469.669</t>
+          <t>9469668540.96931</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10735.843</t>
+          <t>10735843304.2787</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9394.826</t>
+          <t>9394825711.74751</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10937.484</t>
+          <t>10937484049.4849</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>10000.808</t>
+          <t>10000808119.998</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10034.019</t>
+          <t>10034019315.3321</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9654.954</t>
+          <t>9654953637.52796</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>10226.11</t>
+          <t>10226109688.9286</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10420.912</t>
+          <t>10420911801.8709</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>8655.55</t>
+          <t>8655549907.46049</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>8625.534</t>
+          <t>8625533946.94041</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>375790.813</t>
+          <t>375790813413.927</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>421393.291</t>
+          <t>421393290856.26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>413512.445</t>
+          <t>413512445185.402</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>423110.064</t>
+          <t>423110063804.249</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>333406.281</t>
+          <t>333406281224.71</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>321719.619</t>
+          <t>321719619133.684</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>263741.822</t>
+          <t>263741821628.064</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>270868.476</t>
+          <t>270868475633.573</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>276586.183</t>
+          <t>276586183234.603</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>287285.345</t>
+          <t>287285345318.379</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>238203.418</t>
+          <t>238203418300.938</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>198238.679</t>
+          <t>198238679419.592</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>205240.309</t>
+          <t>205240309098.316</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>204407.734</t>
+          <t>204407733571.591</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>202470.146</t>
+          <t>202470145926.776</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2472633.823</t>
+          <t>2472633823372.45</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2238695.615</t>
+          <t>2238695615068.57</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2043512.243</t>
+          <t>2043512242998.07</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1698901.219</t>
+          <t>1698901218870.58</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1533470.626</t>
+          <t>1533470626355.51</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2057319.072</t>
+          <t>2057319071905.59</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2602920.165</t>
+          <t>2602920165022.9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3069586.894</t>
+          <t>3069586893808.66</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>3602649.968</t>
+          <t>3602649967963.23</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>4238212.749</t>
+          <t>4238212749189.03</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>4569366.11</t>
+          <t>4569366109655.62</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4620195.744</t>
+          <t>4620195744478.85</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>4696580.16</t>
+          <t>4696580160233.04</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>4903573.667</t>
+          <t>4903573666997.39</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>5167749.218</t>
+          <t>5167749217767.09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7389.098</t>
+          <t>7389097758.95833</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7536.206</t>
+          <t>7536205723.71416</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4036.322</t>
+          <t>4036322411.57493</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4667.508</t>
+          <t>4667508448.90217</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4939.971</t>
+          <t>4939971073.42936</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5759.486</t>
+          <t>5759486179.68449</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5700.833</t>
+          <t>5700833335.76541</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>5519.844</t>
+          <t>5519844075.33162</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5320.842</t>
+          <t>5320842462.78066</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4830.798</t>
+          <t>4830798097.50484</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>4713.224</t>
+          <t>4713223862.21025</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4811.331</t>
+          <t>4811331387.93465</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>4941.344</t>
+          <t>4941343760.45909</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>12742.465</t>
+          <t>12742464515.5998</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5466.452</t>
+          <t>5466451871.61744</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>71653.491</t>
+          <t>71653490756.5622</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>76836.805</t>
+          <t>76836805060.6692</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76729.378</t>
+          <t>76729378234.1349</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>76431.05</t>
+          <t>76431050278.2063</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>76598.01</t>
+          <t>76598009797.4396</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>79953.188</t>
+          <t>79953188429.3573</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>77389.14</t>
+          <t>77389140498.5642</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>80487.291</t>
+          <t>80487290939.8125</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>92168.27</t>
+          <t>92168269637.1583</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>85036.8</t>
+          <t>85036799636.1935</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>83404.425</t>
+          <t>83404424780.0299</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>83888.948</t>
+          <t>83888947547.1665</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>79816.674</t>
+          <t>79816673997.0802</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>76168.281</t>
+          <t>76168281402.5767</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>70356.751</t>
+          <t>70356750580.5644</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>277949.358</t>
+          <t>277949357665.659</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>248077.951</t>
+          <t>248077950914.189</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>281939.487</t>
+          <t>281939486664.434</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>277469.407</t>
+          <t>277469406568.191</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>251129.901</t>
+          <t>251129901209.623</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>261707.28</t>
+          <t>261707279786.389</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>262345.677</t>
+          <t>262345677133.666</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>233512.332</t>
+          <t>233512332076.239</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>224432.145</t>
+          <t>224432144833.418</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>220479.096</t>
+          <t>220479095500.665</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>216484.699</t>
+          <t>216484699212.122</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>214243.421</t>
+          <t>214243420949.645</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>216515.123</t>
+          <t>216515123499.236</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>208108.145</t>
+          <t>208108144906.556</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>191219.725</t>
+          <t>191219725426.435</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>80538.899</t>
+          <t>80538899381.3859</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>86680.259</t>
+          <t>86680258980.8942</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>88367.405</t>
+          <t>88367404800.4723</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>84548.252</t>
+          <t>84548251818.2961</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>68161.123</t>
+          <t>68161122928.0207</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>68765.265</t>
+          <t>68765264632.6281</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>71749.374</t>
+          <t>71749373678.5177</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>80951.309</t>
+          <t>80951308953.4432</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>82138.479</t>
+          <t>82138479010.5381</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>91655.759</t>
+          <t>91655758578.5031</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>94240.359</t>
+          <t>94240358978.2454</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>97028.852</t>
+          <t>97028851517.5658</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>96247.546</t>
+          <t>96247546219.5918</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>94187.982</t>
+          <t>94187982198.9879</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>96252.003</t>
+          <t>96252003028.5714</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7502.509</t>
+          <t>7502508782.03469</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9968.066</t>
+          <t>9968065903.27227</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2868.728</t>
+          <t>2868727723.92033</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3145.075</t>
+          <t>3145075118.27469</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3214.791</t>
+          <t>3214790651.93577</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2902.031</t>
+          <t>2902031413.3014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2416.588</t>
+          <t>2416588438.51939</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2497.761</t>
+          <t>2497760703.05316</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2687.116</t>
+          <t>2687116045.96619</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2417.651</t>
+          <t>2417650916.50658</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2726.989</t>
+          <t>2726989087.77539</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3073.875</t>
+          <t>3073875446.93331</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2804.973</t>
+          <t>2804973051.49572</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2638.299</t>
+          <t>2638299474.20652</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2667.83</t>
+          <t>2667829606.95432</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>675.737</t>
+          <t>675736853.1242</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>378.248</t>
+          <t>378247922.663061</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>340.588</t>
+          <t>340587736.802584</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>354.581</t>
+          <t>354581269.205976</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>366.637</t>
+          <t>366637441.659819</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>337.861</t>
+          <t>337860660.32593</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>312.499</t>
+          <t>312498732.770399</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>331.726</t>
+          <t>331725630.738931</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>349.879</t>
+          <t>349879303.217409</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>377.85</t>
+          <t>377850497.821315</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>372.178</t>
+          <t>372177609.473163</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>381.558</t>
+          <t>381557810.80985</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>387.688</t>
+          <t>387687601.212287</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>411.104</t>
+          <t>411104075.344983</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>415.977</t>
+          <t>415976798.859438</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2170.334</t>
+          <t>2170333581.75219</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2071.779</t>
+          <t>2071779122.56771</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1811.721</t>
+          <t>1811720565.68107</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1858.075</t>
+          <t>1858074680.78101</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1843.432</t>
+          <t>1843432332.634</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1744.67</t>
+          <t>1744669550.38361</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1500.784</t>
+          <t>1500783936.38709</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1747.156</t>
+          <t>1747156022.80914</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2448.695</t>
+          <t>2448694986.36952</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7354.518</t>
+          <t>7354518097.69244</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>157202.485</t>
+          <t>157202485311.272</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>23266.774</t>
+          <t>23266773919.5997</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1636.14</t>
+          <t>1636140129.1039</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1587.205</t>
+          <t>1587204535.43948</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1251.479</t>
+          <t>1251479082.60337</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>174170.855</t>
+          <t>174170855321.876</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>178507.649</t>
+          <t>178507648851.308</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>180855.104</t>
+          <t>180855104318.867</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>189021.755</t>
+          <t>189021754511.596</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>197128.997</t>
+          <t>197128996723.087</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>208282.673</t>
+          <t>208282672899.488</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>218656.055</t>
+          <t>218656055329.473</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>223804.18</t>
+          <t>223804179929.395</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>226393.022</t>
+          <t>226393022218.981</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>228176.126</t>
+          <t>228176125706.407</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>227935.541</t>
+          <t>227935541477.957</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>244393.692</t>
+          <t>244393691771.333</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>247889.631</t>
+          <t>247889631489.302</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>264728.713</t>
+          <t>264728712700.929</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>252697.272</t>
+          <t>252697272057.659</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1598.365</t>
+          <t>1598365089.97196</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1574.811</t>
+          <t>1574810531.2954</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1542.867</t>
+          <t>1542866612.49504</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1564.784</t>
+          <t>1564784200.85533</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1532.736</t>
+          <t>1532736372.90321</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1418.906</t>
+          <t>1418905750.91379</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1221.951</t>
+          <t>1221950524.7716</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1449.915</t>
+          <t>1449915390.19328</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1418.719</t>
+          <t>1418719370.42281</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1399.658</t>
+          <t>1399657716.19942</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1896.125</t>
+          <t>1896124565.69013</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1515.713</t>
+          <t>1515712964.9143</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1612.682</t>
+          <t>1612681857.02127</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1699.029</t>
+          <t>1699028875.51688</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1707.412</t>
+          <t>1707411967.59856</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>11643.556</t>
+          <t>11643555859.8136</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11104.341</t>
+          <t>11104341460.9943</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10777.102</t>
+          <t>10777101555.4114</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10909.944</t>
+          <t>10909944273.1002</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10706.041</t>
+          <t>10706041308.7894</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>10525.536</t>
+          <t>10525535643.5423</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10160.781</t>
+          <t>10160781073.3566</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>9687.317</t>
+          <t>9687316781.27165</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>9565.274</t>
+          <t>9565274181.44778</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9451.335</t>
+          <t>9451335375.74268</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9324.011</t>
+          <t>9324011066.48369</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>9353.748</t>
+          <t>9353748197.13414</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>9531.401</t>
+          <t>9531400750.9949</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>9662.096</t>
+          <t>9662095878.66803</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>9275.973</t>
+          <t>9275973364.57294</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>54061.111</t>
+          <t>54061110896.1854</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>49100.348</t>
+          <t>49100348324.9031</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47909.99</t>
+          <t>47909989869.6321</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>49822.234</t>
+          <t>49822234490.759</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>52593.633</t>
+          <t>52593633305.2388</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>40315.744</t>
+          <t>40315743532.4611</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>42156.769</t>
+          <t>42156769489.1375</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>44523.139</t>
+          <t>44523139023.8714</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>43387.46</t>
+          <t>43387459559.8838</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>42670.921</t>
+          <t>42670921309.714</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>48712.438</t>
+          <t>48712438306.1273</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>46452.617</t>
+          <t>46452616674.1828</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>43766.885</t>
+          <t>43766885221.739</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>43865.279</t>
+          <t>43865279018.6912</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>44334.528</t>
+          <t>44334528367.2044</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10468.264</t>
+          <t>10468264246.154</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10449.339</t>
+          <t>10449338832.9206</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10526.76</t>
+          <t>10526759696.5224</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10698.785</t>
+          <t>10698785471.5124</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10930.656</t>
+          <t>10930655706.4286</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>11153.378</t>
+          <t>11153378201.2167</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10973.656</t>
+          <t>10973656142.7204</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>10771.947</t>
+          <t>10771946738.6531</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>10281.18</t>
+          <t>10281179696.2877</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>10336.258</t>
+          <t>10336257814.5361</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10146.531</t>
+          <t>10146530707.462</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>9270.263</t>
+          <t>9270263158.21118</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>8857.526</t>
+          <t>8857526001.32777</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>8756.11</t>
+          <t>8756110197.61825</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>8514.919</t>
+          <t>8514918588.18586</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>78918.647</t>
+          <t>78918647430.9232</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>70014.15</t>
+          <t>70014150393.7308</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>69999.857</t>
+          <t>69999857364.9591</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>68706.341</t>
+          <t>68706340718.6801</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>69235.683</t>
+          <t>69235683457.2758</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>67171.576</t>
+          <t>67171575565.7356</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>82857.644</t>
+          <t>82857643952.1178</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>82353.941</t>
+          <t>82353940708.2231</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>85148.701</t>
+          <t>85148700773.961</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>77873.208</t>
+          <t>77873208432.8846</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>72178.011</t>
+          <t>72178011271.1234</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>77846.071</t>
+          <t>77846071078.9997</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>23276.796</t>
+          <t>23276796045.5509</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>24424.381</t>
+          <t>24424380523.9613</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>25522.117</t>
+          <t>25522116811.6138</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>447370.343</t>
+          <t>447370343395.677</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>381095.852</t>
+          <t>381095851671.353</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>323899.408</t>
+          <t>323899408279.928</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>291240.692</t>
+          <t>291240692334.143</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>264683.513</t>
+          <t>264683513090.043</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>264453.123</t>
+          <t>264453122545.747</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>265452.981</t>
+          <t>265452981446.293</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>266582.687</t>
+          <t>266582686512.379</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>263587.713</t>
+          <t>263587713264.257</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>308675.092</t>
+          <t>308675092331.242</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>344914.211</t>
+          <t>344914211103.331</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>331535.968</t>
+          <t>331535968445.708</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>310741.424</t>
+          <t>310741423868.607</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>304054.549</t>
+          <t>304054548808.577</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>271079.896</t>
+          <t>271079896059.415</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3483.702</t>
+          <t>3483702420.79647</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3678.131</t>
+          <t>3678131396.14357</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3384.596</t>
+          <t>3384595958.53138</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3019.417</t>
+          <t>3019416559.81679</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3062.324</t>
+          <t>3062324205.49365</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2840.782</t>
+          <t>2840782280.20501</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2924.952</t>
+          <t>2924952149.42262</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2950.182</t>
+          <t>2950182281.65023</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2860.197</t>
+          <t>2860197498.30564</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>3011.535</t>
+          <t>3011534876.08123</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3106.539</t>
+          <t>3106538847.09142</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3227.683</t>
+          <t>3227683318.12753</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3145.914</t>
+          <t>3145913695.41225</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3872.405</t>
+          <t>3872405243.7944</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3814.899</t>
+          <t>3814899463.83434</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1572.605</t>
+          <t>1572605010.19403</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1608.573</t>
+          <t>1608573335.51296</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1546.612</t>
+          <t>1546612303.21515</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1563.523</t>
+          <t>1563522801.26219</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1508.025</t>
+          <t>1508025361.54996</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1497.615</t>
+          <t>1497614918.24974</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1488.541</t>
+          <t>1488541345.24237</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1501.641</t>
+          <t>1501641488.1651</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1470.137</t>
+          <t>1470136572.31594</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1465.203</t>
+          <t>1465203162.17024</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1468.772</t>
+          <t>1468771675.56691</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1487.845</t>
+          <t>1487845484.45501</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1443.493</t>
+          <t>1443492971.2542</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1556.035</t>
+          <t>1556034597.293</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1448.702</t>
+          <t>1448701510.87399</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5381.392</t>
+          <t>5381391824.60203</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5506.852</t>
+          <t>5506852282.72344</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5387.092</t>
+          <t>5387092140.93919</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5490.29</t>
+          <t>5490289994.89609</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>5682.605</t>
+          <t>5682604777.80184</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5874.535</t>
+          <t>5874535449.51945</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6007.213</t>
+          <t>6007212809.69997</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6010.704</t>
+          <t>6010703694.68137</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5908.483</t>
+          <t>5908483300.80836</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5927.414</t>
+          <t>5927414080.1653</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>5813.128</t>
+          <t>5813128087.68492</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6143.241</t>
+          <t>6143240852.99579</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6195.303</t>
+          <t>6195302899.769</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>6056.673</t>
+          <t>6056673204.73946</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>5828.057</t>
+          <t>5828056926.21779</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>94854.468</t>
+          <t>94854468205.0173</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>94685.019</t>
+          <t>94685019228.5119</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>109869.619</t>
+          <t>109869618668.787</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>114915.17</t>
+          <t>114915170445.598</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>108253.019</t>
+          <t>108253018592.169</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>196452.949</t>
+          <t>196452949170.88</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>252582.093</t>
+          <t>252582093138.391</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>602147.025</t>
+          <t>602147025188.056</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>661744.007</t>
+          <t>661744006504.277</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>668324.777</t>
+          <t>668324777238.291</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>730090.729</t>
+          <t>730090728765.22</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>731793.786</t>
+          <t>731793786430.673</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>704417.208</t>
+          <t>704417207525.651</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>742750.626</t>
+          <t>742750625630.406</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>751571.758</t>
+          <t>751571758324.14</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>26897.603</t>
+          <t>26897603199.5081</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>23479.212</t>
+          <t>23479211902.1984</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>22974.283</t>
+          <t>22974283177.6034</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>22709.896</t>
+          <t>22709896468.2921</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>22028.017</t>
+          <t>22028017213.013</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>22542.263</t>
+          <t>22542263251.6356</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>22445.573</t>
+          <t>22445573374.0289</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>20963.239</t>
+          <t>20963239343.7534</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21095.248</t>
+          <t>21095247711.2988</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>21032.924</t>
+          <t>21032923718.4479</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>22150.293</t>
+          <t>22150292996.9798</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>24835.329</t>
+          <t>24835328665.0834</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>27409.291</t>
+          <t>27409290777.5268</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>29409.911</t>
+          <t>29409910842.6989</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>28384.567</t>
+          <t>28384566785.4685</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>183372.006</t>
+          <t>183372005737.337</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>192524.966</t>
+          <t>192524965604.677</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>190848.383</t>
+          <t>190848383317.561</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>187861.839</t>
+          <t>187861838988.385</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>216340.334</t>
+          <t>216340333540.067</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>218014.974</t>
+          <t>218014973651.99</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>223778.886</t>
+          <t>223778886180.546</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>226506.116</t>
+          <t>226506115804.74</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>241259.081</t>
+          <t>241259081015.586</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>212715.071</t>
+          <t>212715070503.805</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>215221.604</t>
+          <t>215221604284.17</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>222776.097</t>
+          <t>222776096938.505</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>207593.727</t>
+          <t>207593726639.902</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>205981.194</t>
+          <t>205981194284.493</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>187287.128</t>
+          <t>187287128158.88</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>56704821.218</t>
+          <t>56704821217850.9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>55166197.675</t>
+          <t>55166197675336.5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>57353454.387</t>
+          <t>57353454386708.4</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>59482125.054</t>
+          <t>59482125053564.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>66224482.967</t>
+          <t>66224482967114</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>84350552.123</t>
+          <t>84350552123029</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>87712020.116</t>
+          <t>87712020116141.5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>85432649.606</t>
+          <t>85432649605690.1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>92851839.938</t>
+          <t>92851839937638.7</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>93270197.19</t>
+          <t>93270197190304.5</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>100452121.405</t>
+          <t>100452121405482</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>101728552.526</t>
+          <t>101728552525690</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>87773191.731</t>
+          <t>87773191731408.8</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>86168749.315</t>
+          <t>86168749315064.2</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>71351538.992</t>
+          <t>71351538991837.4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>68206170.047</t>
+          <t>68206170047108.8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>66387925.311</t>
+          <t>66387925310883.5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>67703757.837</t>
+          <t>67703757837436.5</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>68974973.063</t>
+          <t>68974973062623.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>74760365.281</t>
+          <t>74760365280862.2</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>93546385.38</t>
+          <t>93546385380205.4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>98160686.377</t>
+          <t>98160686376941</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>97059432.267</t>
+          <t>97059432267316</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>105732265.971</t>
+          <t>105732265970729</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>107808606.143</t>
+          <t>107808606142702</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>115948518.928</t>
+          <t>115948518927944</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>116968435.818</t>
+          <t>116968435818086</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>103657070.797</t>
+          <t>103657070796893</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>102552245.874</t>
+          <t>102552245874244</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>87878536.47</t>
+          <t>87878536469827.8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
